--- a/docs/test-cases-auth.xlsx
+++ b/docs/test-cases-auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\AIPETCLIENT\leBotChatClient\le-bot-frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DDA052-AD66-4FAB-BC30-6D3675F6C1E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6592B496-B1FF-4271-A108-C34EE44D6ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="314">
   <si>
     <t>用例编号</t>
   </si>
@@ -1075,6 +1075,10 @@
   </si>
   <si>
     <t>无法测试，等手机测试</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1711,7 +1715,9 @@
       <c r="G4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="15" t="s">
+        <v>313</v>
+      </c>
       <c r="I4" s="2" t="s">
         <v>18</v>
       </c>

--- a/docs/test-cases-auth.xlsx
+++ b/docs/test-cases-auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\AIPETCLIENT\leBotChatClient\le-bot-frontend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6592B496-B1FF-4271-A108-C34EE44D6ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E11A22-A808-4E41-95AA-E37A97594422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="317">
   <si>
     <t>用例编号</t>
   </si>
@@ -1079,6 +1079,17 @@
   </si>
   <si>
     <t>完成</t>
+  </si>
+  <si>
+    <t>完成</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fail</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1220,7 +1231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1269,6 +1280,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1716,7 +1736,7 @@
         <v>30</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>18</v>
@@ -1750,7 +1770,9 @@
       <c r="G5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="6"/>
+      <c r="H5" s="17" t="s">
+        <v>314</v>
+      </c>
       <c r="I5" s="2" t="s">
         <v>18</v>
       </c>
@@ -1781,7 +1803,9 @@
       <c r="G6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="17" t="s">
+        <v>314</v>
+      </c>
       <c r="I6" s="2" t="s">
         <v>18</v>
       </c>
@@ -1812,7 +1836,9 @@
       <c r="G7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="18" t="s">
+        <v>313</v>
+      </c>
       <c r="I7" s="2" t="s">
         <v>18</v>
       </c>
@@ -1843,7 +1869,9 @@
       <c r="G8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="18" t="s">
+        <v>313</v>
+      </c>
       <c r="I8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1876,7 +1904,9 @@
       <c r="G9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="18" t="s">
+        <v>313</v>
+      </c>
       <c r="I9" s="2" t="s">
         <v>18</v>
       </c>
@@ -1907,7 +1937,9 @@
       <c r="G10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I10" s="2" t="s">
         <v>18</v>
       </c>
@@ -1938,7 +1970,9 @@
       <c r="G11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="18" t="s">
+        <v>314</v>
+      </c>
       <c r="I11" s="2" t="s">
         <v>18</v>
       </c>
@@ -1969,7 +2003,9 @@
       <c r="G12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="18" t="s">
+        <v>314</v>
+      </c>
       <c r="I12" s="2" t="s">
         <v>18</v>
       </c>
@@ -2000,7 +2036,9 @@
       <c r="G13" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="19" t="s">
+        <v>315</v>
+      </c>
       <c r="I13" s="2" t="s">
         <v>18</v>
       </c>
@@ -2033,7 +2071,9 @@
       <c r="G14" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I14" s="2" t="s">
         <v>18</v>
       </c>
@@ -2066,7 +2106,9 @@
       <c r="G15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I15" s="2" t="s">
         <v>18</v>
       </c>
@@ -2099,7 +2141,9 @@
       <c r="G16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I16" s="2" t="s">
         <v>18</v>
       </c>
@@ -2132,7 +2176,9 @@
       <c r="G17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H17" s="6"/>
+      <c r="H17" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I17" s="2" t="s">
         <v>18</v>
       </c>
@@ -2163,7 +2209,9 @@
       <c r="G18" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="6"/>
+      <c r="H18" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I18" s="2" t="s">
         <v>18</v>
       </c>
@@ -2194,7 +2242,9 @@
       <c r="G19" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="H19" s="6"/>
+      <c r="H19" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2225,7 +2275,9 @@
       <c r="G20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I20" s="2" t="s">
         <v>18</v>
       </c>
@@ -2256,7 +2308,9 @@
       <c r="G21" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="17" t="s">
+        <v>316</v>
+      </c>
       <c r="I21" s="2" t="s">
         <v>18</v>
       </c>
@@ -2318,7 +2372,9 @@
       <c r="G23" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I23" s="2" t="s">
         <v>18</v>
       </c>
@@ -2380,7 +2436,9 @@
       <c r="G25" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="15" t="s">
+        <v>314</v>
+      </c>
       <c r="I25" s="2" t="s">
         <v>18</v>
       </c>
